--- a/pensum/ma03/MA03_Klasseoppgaver_v5.xlsx
+++ b/pensum/ma03/MA03_Klasseoppgaver_v5.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="153">
   <si>
     <t xml:space="preserve">Klasseoppgaver til Markedsføring kapittel 3: Markedsplanen (V5)</t>
   </si>
@@ -149,18 +149,48 @@
     <t xml:space="preserve">a)  Hva er hovedmålet i kroner? Omsetningen i fjor ganger 1 pluss vekstmålet.</t>
   </si>
   <si>
+    <t xml:space="preserve">Formel og begrep</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mål i kroner = utgangspunkt × (1 + vekst). Hovedmålet er toppen i et hierarkisk målsystem, som Byggmester X' mål om minst 8 % vekst (Markedsføring 3.4).</t>
+  </si>
+  <si>
     <t xml:space="preserve">b)  Hva blir omsetningen hvis delmålene nås? Antall anlegg ganger pris pluss antall ladepunkt ganger pris.</t>
   </si>
   <si>
+    <t xml:space="preserve">Omsetning = antall × pris, summert over produktene. Innbyrdes samsvar: delmålene skal til sammen nå hovedmålet (Markedsføring 3.4).</t>
+  </si>
+  <si>
     <t xml:space="preserve">c)  Hvor mange flere montørtimer i året krever delmålene enn det avdelingen solgte i fjor? Anlegg 14 timer, ladepunkt 2 timer.</t>
   </si>
   <si>
+    <t xml:space="preserve">Timebehov = antall × timer per enhet. Realistisk mål: bedriften må ha kapasitet til å nå det (Markedsføring 3.4).</t>
+  </si>
+  <si>
     <t xml:space="preserve">d)  Kari har skrevet tre setninger om avdelingen. Hvilken av dem er et markedsmål etter lærebokas krav (tallfestet, realistisk, hierarkisk, i samsvar)?   A: «Vi skal bli den foretrukne leverandøren av solceller i bydelen.»   B: «Vi skal selge 42 solcelleanlegg i år, mot 34 i fjor. Ida følger opp hver måned.»   C: «Vi skal satse mer på borettslag, for der ligger pengene.»   (skriv bokstaven)</t>
   </si>
   <si>
     <t xml:space="preserve">e)  Nye solkraftanlegg i Norge falt fra 149 MW i 2024 til 117 MW i 2025 (−21,5 %). Er delmålet på 42 solcelleanlegg realistisk? Skriv to setninger og ett tiltak.</t>
   </si>
   <si>
+    <t xml:space="preserve">Realistiske markedsmål (Markedsføring 3.4); markedsplanen må revideres jevnlig (innledningen til kap. 3). Dekningsbidrag per knapp faktor er fra Økonomistyring kap. 7, ikke fra Markedsføring kap. 3.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hint, hvis du står fast</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fra mål til kroner</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hovedmålet: 3 335 640 × 1,20. Delmålene: antall × pris for anlegg, pluss antall × pris for ladepunkt. Bærer delmålene, er summen minst like stor som hovedmålet.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Timene</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Regn timene i fjor (34 × 14 + 180 × 2) og ved målet (42 × 14 + 215 × 2). Forskjellen er det målet krever ekstra. Sammenlikn med de 14 400 timene Nordlys fakturerer.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kilde: Hjertnes, F.: Markedsføring, organisasjon og ledelse for LØM-emnet, kap. 3, avsnitt 3.4 (markedsmål) og kap. 10.3. Tallene er de samme som i appen og sammendraget til kapittel 3. Nordlys Elektro AS er en konstruert casebedrift.</t>
   </si>
   <si>
@@ -257,12 +287,30 @@
     <t xml:space="preserve">c)  Hvor stor markedsandel hadde Fjell på ladepunkt i boliger i Oslo øst i fjor? Fjells antall delt på hele markedet, i prosent med én desimal.</t>
   </si>
   <si>
+    <t xml:space="preserve">Markedsandel = eget salg / hele markedets salg × 100. Boka bruker begrepet i 3.6.1 og 3.7.1, men gir ingen egen formel i kap. 3.</t>
+  </si>
+  <si>
     <t xml:space="preserve">d)  Fjell fikk ingen søkere til en tredje montørstilling fordi bransjen mangler fagarbeidere. Hvor hører mangelen på fagarbeidere hjemme i situasjonsanalysen?   A: Svak side: det er Fjells egen feil   B: Trussel: tilgang på arbeidskraft er en ekstern arbeidsbetingelse   C: Ingen steder: det er ikke markedsføring   (skriv bokstaven)</t>
   </si>
   <si>
     <t xml:space="preserve">e)  Boka sier at bedriften skal utnytte de sterke sidene best mulig og la de svake hemme minst mulig. Hvilken sterk side skal Fjell bygge markedsplanen på, og hvilken svak side må Mona gjøre noe med først? To setninger.</t>
   </si>
   <si>
+    <t xml:space="preserve">En vellykket tilpasning utnytter de sterke sidene best mulig og lar de svake hemme minst mulig (Markedsføring 3.3). Kap. 10.2 legger til at svake sider forbedres så langt det er mulig, og at muligheter utnyttes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Internt eller eksternt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spør for hver post: rår Fjell over dette selv? Kompetanse, margin og antall montører er internt. Markedet, konkurrentene og tilgangen på arbeidskraft er eksternt (3.3).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Markedsandelen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fjells antall delt på hele markedet, ganger 100: 48 av 1 600. Forretningsidéen: se etter setningen som har produkt, marked og særpreg.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kilde: Hjertnes, F.: Markedsføring, organisasjon og ledelse for LØM-emnet, kap. 3, avsnitt 3.2 (forretningsidé) og 3.3 (situasjonsanalyse), kap. 10.2 (SOFT-analyse). Elbilandelen: Elbilforeningen, årsberetning 2025. Fjell Elektro AS er en konstruert casebedrift; markedstallene for Oslo øst er konstruerte.</t>
   </si>
   <si>
@@ -326,6 +374,21 @@
     <t xml:space="preserve">e)  Hvilket av de fire forslagene anbefaler du Kari, og hvilken av Porters tre konkurransestrategier passer til det? Begrunn med minst ett tall eller faktum fra situasjonsanalysen. Tre setninger.</t>
   </si>
   <si>
+    <t xml:space="preserve">Produkt/markeds-matrisen og integrasjon (Markedsføring 3.6), Porters tre konkurransestrategier og advarselen mot uklar profil (3.7).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hva er nytt?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Spør: er produktet nytt for avdelingen? Er kundene nye? Bare nytt produkt er produktutvikling. Bare nye kunder er markedsutvikling. Begge er diversifisering.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Integrasjon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Samme nivå i verdikjeden er horisontal. Et annet nivå er vertikal: baklengs når du kjøper leddet før deg (leverandøren), forlengs når du kjøper leddet nærmere kunden.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kilde: Hjertnes, F.: Markedsføring, organisasjon og ledelse for LØM-emnet, kap. 3, avsnitt 3.6 (vekststrategier og integrasjon, figur 3.3) og 3.7 (Porters konkurransestrategier). Nordlys Elektro AS er en konstruert casebedrift.</t>
   </si>
   <si>
@@ -383,16 +446,40 @@
     <t xml:space="preserve">a)  Hvor mange ladepunkt ventes montert i boliger i Oslo øst i år? Markedet i fjor ganger 1 pluss markedsveksten.</t>
   </si>
   <si>
+    <t xml:space="preserve">Marked i år = marked i fjor × (1 + markedsvekst). Grunnlaget for et mål om markedsandel (Markedsføring 3.4 og 3.6.1).</t>
+  </si>
+  <si>
     <t xml:space="preserve">b)  Hvor mange ladepunkt må Fjell montere i år for å ha 5 % markedsandel?</t>
   </si>
   <si>
+    <t xml:space="preserve">Antall = marked × markedsandel. Timebehov = antall × timer per enhet. Realistisk mål: kapasitet og marked (Markedsføring 3.4).</t>
+  </si>
+  <si>
     <t xml:space="preserve">c)  Hvor mange prosent må Fjell øke antall ladepunkt fra i fjor for å nå målet? Svar med én desimal.</t>
   </si>
   <si>
+    <t xml:space="preserve">Vekst i prosent = (nytt tall / gammelt tall − 1) × 100. Markedsinntrengning betyr at markedsandelen øker (Markedsføring 3.6.1).</t>
+  </si>
+  <si>
     <t xml:space="preserve">d)  Tenk deg at Fjell vokser 15 %, like mye som markedet, og monterer 55 ladepunkt. Hva skjer med markedsandelen?   A: Den øker, fordi Fjell vokser   B: Den blir omtrent den samme, 3,0 %   C: Den synker til under 2 %   (skriv bokstaven)</t>
   </si>
   <si>
     <t xml:space="preserve">e)  Er målet om 5 % markedsandel realistisk for Fjell, og hvilken av Porters strategier passer? Bruk tallene du har regnet. To–tre setninger.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Realistiske, tallfestede mål knyttet til tidspunkt (Markedsføring 3.4, 10.3); kostnadslederskap krever høy markedsandel (3.7.1); fokusering og nisje (3.7.3).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fra andel til antall</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Markedet i år: 1 600 × 1,15. Målet i antall: markedet i år × 0,05. Veksten for Fjell: målet delt på 48, minus 1.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Andelen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Markedsandel = Fjells antall / markedets antall. Vokser begge med 15 %, blir brøken den samme. Prøv med 55 / 1 840.</t>
   </si>
   <si>
     <t xml:space="preserve">Kilde: Hjertnes, F.: Markedsføring, organisasjon og ledelse for LØM-emnet, kap. 3, avsnitt 3.4 (markedsmål), 3.6.1 (markedsinntrengning: markedsandelene øker) og 3.7 (Porter). Fjell Elektro AS er en konstruert casebedrift; markedstallene for Oslo øst er konstruerte.</t>
@@ -406,7 +493,7 @@
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0.##;\−#,##0.##;\0"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="13">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -473,8 +560,30 @@
       <family val="0"/>
       <charset val="1"/>
     </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FF2F4A6D"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -490,13 +599,31 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFF4F6FA"/>
-        <bgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFEEF2F8"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
         <bgColor rgb="FFFFFF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEEF2F8"/>
+        <bgColor rgb="FFF4F6FA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB8954A"/>
+        <bgColor rgb="FF808080"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBF6EA"/>
+        <bgColor rgb="FFF4F6FA"/>
       </patternFill>
     </fill>
   </fills>
@@ -549,7 +676,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="26">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -622,11 +749,31 @@
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -663,8 +810,8 @@
       <rgbColor rgb="FF808080"/>
       <rgbColor rgb="FF9999FF"/>
       <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFF4F6FA"/>
-      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFFBF6EA"/>
+      <rgbColor rgb="FFEEF2F8"/>
       <rgbColor rgb="FF660066"/>
       <rgbColor rgb="FFFF8080"/>
       <rgbColor rgb="FF0066CC"/>
@@ -678,7 +825,7 @@
       <rgbColor rgb="FF008080"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFCCFFFF"/>
+      <rgbColor rgb="FFF4F6FA"/>
       <rgbColor rgb="FFCCFFCC"/>
       <rgbColor rgb="FFFFFF99"/>
       <rgbColor rgb="FF99CCFF"/>
@@ -692,7 +839,7 @@
       <rgbColor rgb="FFFF9900"/>
       <rgbColor rgb="FFFF6600"/>
       <rgbColor rgb="FF5E6670"/>
-      <rgbColor rgb="FF969696"/>
+      <rgbColor rgb="FFB8954A"/>
       <rgbColor rgb="FF003366"/>
       <rgbColor rgb="FF339966"/>
       <rgbColor rgb="FF003300"/>
@@ -995,7 +1142,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
@@ -1160,35 +1307,20 @@
         <v/>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="7" t="s">
+    <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="15"/>
-      <c r="G19" s="17" t="str">
-        <f aca="false">IF(F19="","",IF(ABS(F19-(4055570))&lt;=1,"Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="7" t="s">
+      <c r="B19" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="15"/>
-      <c r="G20" s="17" t="str">
-        <f aca="false">IF(F20="","",IF(ABS(F20-(182))&lt;=0.000000001,"Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="78.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="C19" s="19"/>
+      <c r="D19" s="19"/>
+      <c r="E19" s="19"/>
+      <c r="F19" s="19"/>
+      <c r="G19" s="19"/>
+    </row>
+    <row r="21" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
         <v>43</v>
       </c>
@@ -1196,84 +1328,195 @@
       <c r="C21" s="7"/>
       <c r="D21" s="7"/>
       <c r="E21" s="7"/>
-      <c r="F21" s="18"/>
+      <c r="F21" s="15"/>
       <c r="G21" s="17" t="str">
-        <f aca="false">IF(F21="","",IF(UPPER(TRIM(F21))="B","Riktig","Prøv igjen"))</f>
+        <f aca="false">IF(F21="","",IF(ABS(F21-(4055570))&lt;=1,"Riktig","Prøv igjen"))</f>
         <v/>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="7" t="s">
+    <row r="22" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="B22" s="19" t="s">
         <v>44</v>
       </c>
-      <c r="B22" s="7"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="19"/>
-      <c r="B23" s="19"/>
-      <c r="C23" s="19"/>
-      <c r="D23" s="19"/>
-      <c r="E23" s="19"/>
-      <c r="F23" s="19"/>
-      <c r="G23" s="19"/>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="19"/>
-      <c r="B24" s="19"/>
-      <c r="C24" s="19"/>
-      <c r="D24" s="19"/>
-      <c r="E24" s="19"/>
-      <c r="F24" s="19"/>
-      <c r="G24" s="19"/>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="19"/>
-      <c r="B25" s="19"/>
+      <c r="C22" s="19"/>
+      <c r="D22" s="19"/>
+      <c r="E22" s="19"/>
+      <c r="F22" s="19"/>
+      <c r="G22" s="19"/>
+    </row>
+    <row r="24" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="B24" s="7"/>
+      <c r="C24" s="7"/>
+      <c r="D24" s="7"/>
+      <c r="E24" s="7"/>
+      <c r="F24" s="15"/>
+      <c r="G24" s="17" t="str">
+        <f aca="false">IF(F24="","",IF(ABS(F24-(182))&lt;=0.000000001,"Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="B25" s="19" t="s">
+        <v>46</v>
+      </c>
       <c r="C25" s="19"/>
       <c r="D25" s="19"/>
       <c r="E25" s="19"/>
       <c r="F25" s="19"/>
       <c r="G25" s="19"/>
     </row>
-    <row r="27" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="6" t="s">
-        <v>45</v>
-      </c>
-      <c r="B27" s="6"/>
-      <c r="C27" s="6"/>
-      <c r="D27" s="6"/>
-      <c r="E27" s="6"/>
-      <c r="F27" s="6"/>
-      <c r="G27" s="6"/>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="B28" s="6"/>
-      <c r="C28" s="6"/>
-      <c r="D28" s="6"/>
-      <c r="E28" s="6"/>
-      <c r="F28" s="6"/>
-      <c r="G28" s="6"/>
+    <row r="27" customFormat="false" ht="78.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="B27" s="7"/>
+      <c r="C27" s="7"/>
+      <c r="D27" s="7"/>
+      <c r="E27" s="7"/>
+      <c r="F27" s="20"/>
+      <c r="G27" s="17" t="str">
+        <f aca="false">IF(F27="","",IF(UPPER(TRIM(F27))="B","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="B28" s="7"/>
+      <c r="C28" s="7"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="7"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="21"/>
+      <c r="B29" s="21"/>
+      <c r="C29" s="21"/>
+      <c r="D29" s="21"/>
+      <c r="E29" s="21"/>
+      <c r="F29" s="21"/>
+      <c r="G29" s="21"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="21"/>
+      <c r="B30" s="21"/>
+      <c r="C30" s="21"/>
+      <c r="D30" s="21"/>
+      <c r="E30" s="21"/>
+      <c r="F30" s="21"/>
+      <c r="G30" s="21"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="21"/>
+      <c r="B31" s="21"/>
+      <c r="C31" s="21"/>
+      <c r="D31" s="21"/>
+      <c r="E31" s="21"/>
+      <c r="F31" s="21"/>
+      <c r="G31" s="21"/>
+    </row>
+    <row r="32" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="B32" s="19" t="s">
+        <v>49</v>
+      </c>
+      <c r="C32" s="19"/>
+      <c r="D32" s="19"/>
+      <c r="E32" s="19"/>
+      <c r="F32" s="19"/>
+      <c r="G32" s="19"/>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="22" t="s">
+        <v>50</v>
+      </c>
+      <c r="B35" s="22"/>
+      <c r="C35" s="22"/>
+      <c r="D35" s="22"/>
+      <c r="E35" s="22"/>
+      <c r="F35" s="22"/>
+      <c r="G35" s="22"/>
+    </row>
+    <row r="36" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="23" t="s">
+        <v>51</v>
+      </c>
+      <c r="B36" s="24" t="s">
+        <v>52</v>
+      </c>
+      <c r="C36" s="24"/>
+      <c r="D36" s="24"/>
+      <c r="E36" s="24"/>
+      <c r="F36" s="24"/>
+      <c r="G36" s="24"/>
+    </row>
+    <row r="37" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="23" t="s">
+        <v>53</v>
+      </c>
+      <c r="B37" s="24" t="s">
+        <v>54</v>
+      </c>
+      <c r="C37" s="24"/>
+      <c r="D37" s="24"/>
+      <c r="E37" s="24"/>
+      <c r="F37" s="24"/>
+      <c r="G37" s="24"/>
+    </row>
+    <row r="39" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="B39" s="6"/>
+      <c r="C39" s="6"/>
+      <c r="D39" s="6"/>
+      <c r="E39" s="6"/>
+      <c r="F39" s="6"/>
+      <c r="G39" s="6"/>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B40" s="6"/>
+      <c r="C40" s="6"/>
+      <c r="D40" s="6"/>
+      <c r="E40" s="6"/>
+      <c r="F40" s="6"/>
+      <c r="G40" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="19">
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A15:G15"/>
     <mergeCell ref="A17:E17"/>
     <mergeCell ref="A18:E18"/>
-    <mergeCell ref="A19:E19"/>
-    <mergeCell ref="A20:E20"/>
+    <mergeCell ref="B19:G19"/>
     <mergeCell ref="A21:E21"/>
-    <mergeCell ref="A22:E22"/>
-    <mergeCell ref="A23:G25"/>
-    <mergeCell ref="A27:G27"/>
-    <mergeCell ref="A28:G28"/>
+    <mergeCell ref="B22:G22"/>
+    <mergeCell ref="A24:E24"/>
+    <mergeCell ref="B25:G25"/>
+    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A29:G31"/>
+    <mergeCell ref="B32:G32"/>
+    <mergeCell ref="A35:G35"/>
+    <mergeCell ref="B36:G36"/>
+    <mergeCell ref="B37:G37"/>
+    <mergeCell ref="A39:G39"/>
+    <mergeCell ref="A40:G40"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1290,7 +1533,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:G42"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
@@ -1301,7 +1544,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1311,7 +1554,7 @@
     </row>
     <row r="4" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -1322,7 +1565,7 @@
     </row>
     <row r="5" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -1333,10 +1576,10 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="16" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="C7" s="16"/>
       <c r="D7" s="16"/>
@@ -1345,11 +1588,11 @@
       <c r="G7" s="16"/>
     </row>
     <row r="8" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="20" t="s">
-        <v>52</v>
+      <c r="A8" s="25" t="s">
+        <v>62</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>53</v>
+        <v>63</v>
       </c>
       <c r="C8" s="7"/>
       <c r="D8" s="7"/>
@@ -1358,11 +1601,11 @@
       <c r="G8" s="7"/>
     </row>
     <row r="9" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="20" t="s">
-        <v>54</v>
+      <c r="A9" s="25" t="s">
+        <v>64</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
@@ -1371,11 +1614,11 @@
       <c r="G9" s="7"/>
     </row>
     <row r="10" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="20" t="s">
-        <v>56</v>
+      <c r="A10" s="25" t="s">
+        <v>66</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="C10" s="7"/>
       <c r="D10" s="7"/>
@@ -1384,11 +1627,11 @@
       <c r="G10" s="7"/>
     </row>
     <row r="11" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="20" t="s">
-        <v>58</v>
+      <c r="A11" s="25" t="s">
+        <v>68</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="C11" s="7"/>
       <c r="D11" s="7"/>
@@ -1397,11 +1640,11 @@
       <c r="G11" s="7"/>
     </row>
     <row r="12" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="20" t="s">
-        <v>60</v>
+      <c r="A12" s="25" t="s">
+        <v>70</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>61</v>
+        <v>71</v>
       </c>
       <c r="C12" s="7"/>
       <c r="D12" s="7"/>
@@ -1410,11 +1653,11 @@
       <c r="G12" s="7"/>
     </row>
     <row r="13" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="20" t="s">
-        <v>62</v>
+      <c r="A13" s="25" t="s">
+        <v>72</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>63</v>
+        <v>73</v>
       </c>
       <c r="C13" s="7"/>
       <c r="D13" s="7"/>
@@ -1423,11 +1666,11 @@
       <c r="G13" s="7"/>
     </row>
     <row r="14" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="20" t="s">
-        <v>64</v>
+      <c r="A14" s="25" t="s">
+        <v>74</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>65</v>
+        <v>75</v>
       </c>
       <c r="C14" s="7"/>
       <c r="D14" s="7"/>
@@ -1436,11 +1679,11 @@
       <c r="G14" s="7"/>
     </row>
     <row r="15" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="20" t="s">
-        <v>66</v>
+      <c r="A15" s="25" t="s">
+        <v>76</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>67</v>
+        <v>77</v>
       </c>
       <c r="C15" s="7"/>
       <c r="D15" s="7"/>
@@ -1465,13 +1708,13 @@
     </row>
     <row r="18" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>68</v>
+        <v>78</v>
       </c>
       <c r="B18" s="7"/>
       <c r="C18" s="7"/>
       <c r="D18" s="7"/>
       <c r="E18" s="7"/>
-      <c r="F18" s="18"/>
+      <c r="F18" s="20"/>
       <c r="G18" s="17" t="str">
         <f aca="false">IF(F18="","",IF(UPPER(TRIM(F18))="C","Riktig","Prøv igjen"))</f>
         <v/>
@@ -1479,7 +1722,7 @@
     </row>
     <row r="19" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>69</v>
+        <v>79</v>
       </c>
       <c r="B19" s="7"/>
       <c r="C19" s="7"/>
@@ -1488,13 +1731,13 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="B20" s="7"/>
       <c r="C20" s="7"/>
       <c r="D20" s="7"/>
       <c r="E20" s="7"/>
-      <c r="F20" s="18"/>
+      <c r="F20" s="20"/>
       <c r="G20" s="17" t="str">
         <f aca="false">IF(F20="","",IF(UPPER(TRIM(F20))="JA","Riktig","Prøv igjen"))</f>
         <v/>
@@ -1502,13 +1745,13 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
-        <v>71</v>
+        <v>81</v>
       </c>
       <c r="B21" s="7"/>
       <c r="C21" s="7"/>
       <c r="D21" s="7"/>
       <c r="E21" s="7"/>
-      <c r="F21" s="18"/>
+      <c r="F21" s="20"/>
       <c r="G21" s="17" t="str">
         <f aca="false">IF(F21="","",IF(UPPER(TRIM(F21))="JA","Riktig","Prøv igjen"))</f>
         <v/>
@@ -1516,13 +1759,13 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="7" t="s">
-        <v>72</v>
+        <v>82</v>
       </c>
       <c r="B22" s="7"/>
       <c r="C22" s="7"/>
       <c r="D22" s="7"/>
       <c r="E22" s="7"/>
-      <c r="F22" s="18"/>
+      <c r="F22" s="20"/>
       <c r="G22" s="17" t="str">
         <f aca="false">IF(F22="","",IF(UPPER(TRIM(F22))="JA","Riktig","Prøv igjen"))</f>
         <v/>
@@ -1530,13 +1773,13 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="7" t="s">
-        <v>73</v>
+        <v>83</v>
       </c>
       <c r="B23" s="7"/>
       <c r="C23" s="7"/>
       <c r="D23" s="7"/>
       <c r="E23" s="7"/>
-      <c r="F23" s="18"/>
+      <c r="F23" s="20"/>
       <c r="G23" s="17" t="str">
         <f aca="false">IF(F23="","",IF(UPPER(TRIM(F23))="NEI","Riktig","Prøv igjen"))</f>
         <v/>
@@ -1544,13 +1787,13 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="7" t="s">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="B24" s="7"/>
       <c r="C24" s="7"/>
       <c r="D24" s="7"/>
       <c r="E24" s="7"/>
-      <c r="F24" s="18"/>
+      <c r="F24" s="20"/>
       <c r="G24" s="17" t="str">
         <f aca="false">IF(F24="","",IF(UPPER(TRIM(F24))="NEI","Riktig","Prøv igjen"))</f>
         <v/>
@@ -1558,13 +1801,13 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="7" t="s">
-        <v>75</v>
+        <v>85</v>
       </c>
       <c r="B25" s="7"/>
       <c r="C25" s="7"/>
       <c r="D25" s="7"/>
       <c r="E25" s="7"/>
-      <c r="F25" s="18"/>
+      <c r="F25" s="20"/>
       <c r="G25" s="17" t="str">
         <f aca="false">IF(F25="","",IF(UPPER(TRIM(F25))="NEI","Riktig","Prøv igjen"))</f>
         <v/>
@@ -1572,7 +1815,7 @@
     </row>
     <row r="26" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="7" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="B26" s="7"/>
       <c r="C26" s="7"/>
@@ -1584,80 +1827,143 @@
         <v/>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="B27" s="7"/>
-      <c r="C27" s="7"/>
-      <c r="D27" s="7"/>
-      <c r="E27" s="7"/>
-      <c r="F27" s="18"/>
-      <c r="G27" s="17" t="str">
-        <f aca="false">IF(F27="","",IF(UPPER(TRIM(F27))="B","Riktig","Prøv igjen"))</f>
+    <row r="27" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="B27" s="19" t="s">
+        <v>87</v>
+      </c>
+      <c r="C27" s="19"/>
+      <c r="D27" s="19"/>
+      <c r="E27" s="19"/>
+      <c r="F27" s="19"/>
+      <c r="G27" s="19"/>
+    </row>
+    <row r="29" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="B29" s="7"/>
+      <c r="C29" s="7"/>
+      <c r="D29" s="7"/>
+      <c r="E29" s="7"/>
+      <c r="F29" s="20"/>
+      <c r="G29" s="17" t="str">
+        <f aca="false">IF(F29="","",IF(UPPER(TRIM(F29))="B","Riktig","Prøv igjen"))</f>
         <v/>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="7" t="s">
-        <v>78</v>
-      </c>
-      <c r="B28" s="7"/>
-      <c r="C28" s="7"/>
-      <c r="D28" s="7"/>
-      <c r="E28" s="7"/>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="19"/>
-      <c r="B29" s="19"/>
-      <c r="C29" s="19"/>
-      <c r="D29" s="19"/>
-      <c r="E29" s="19"/>
-      <c r="F29" s="19"/>
-      <c r="G29" s="19"/>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="19"/>
-      <c r="B30" s="19"/>
-      <c r="C30" s="19"/>
-      <c r="D30" s="19"/>
-      <c r="E30" s="19"/>
-      <c r="F30" s="19"/>
-      <c r="G30" s="19"/>
+    <row r="30" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="B30" s="7"/>
+      <c r="C30" s="7"/>
+      <c r="D30" s="7"/>
+      <c r="E30" s="7"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="19"/>
-      <c r="B31" s="19"/>
-      <c r="C31" s="19"/>
-      <c r="D31" s="19"/>
-      <c r="E31" s="19"/>
-      <c r="F31" s="19"/>
-      <c r="G31" s="19"/>
-    </row>
-    <row r="33" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="6" t="s">
-        <v>79</v>
-      </c>
-      <c r="B33" s="6"/>
-      <c r="C33" s="6"/>
-      <c r="D33" s="6"/>
-      <c r="E33" s="6"/>
-      <c r="F33" s="6"/>
-      <c r="G33" s="6"/>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="B34" s="6"/>
-      <c r="C34" s="6"/>
-      <c r="D34" s="6"/>
-      <c r="E34" s="6"/>
-      <c r="F34" s="6"/>
-      <c r="G34" s="6"/>
+      <c r="A31" s="21"/>
+      <c r="B31" s="21"/>
+      <c r="C31" s="21"/>
+      <c r="D31" s="21"/>
+      <c r="E31" s="21"/>
+      <c r="F31" s="21"/>
+      <c r="G31" s="21"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="21"/>
+      <c r="B32" s="21"/>
+      <c r="C32" s="21"/>
+      <c r="D32" s="21"/>
+      <c r="E32" s="21"/>
+      <c r="F32" s="21"/>
+      <c r="G32" s="21"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="21"/>
+      <c r="B33" s="21"/>
+      <c r="C33" s="21"/>
+      <c r="D33" s="21"/>
+      <c r="E33" s="21"/>
+      <c r="F33" s="21"/>
+      <c r="G33" s="21"/>
+    </row>
+    <row r="34" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="B34" s="19" t="s">
+        <v>90</v>
+      </c>
+      <c r="C34" s="19"/>
+      <c r="D34" s="19"/>
+      <c r="E34" s="19"/>
+      <c r="F34" s="19"/>
+      <c r="G34" s="19"/>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="22" t="s">
+        <v>50</v>
+      </c>
+      <c r="B37" s="22"/>
+      <c r="C37" s="22"/>
+      <c r="D37" s="22"/>
+      <c r="E37" s="22"/>
+      <c r="F37" s="22"/>
+      <c r="G37" s="22"/>
+    </row>
+    <row r="38" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="23" t="s">
+        <v>91</v>
+      </c>
+      <c r="B38" s="24" t="s">
+        <v>92</v>
+      </c>
+      <c r="C38" s="24"/>
+      <c r="D38" s="24"/>
+      <c r="E38" s="24"/>
+      <c r="F38" s="24"/>
+      <c r="G38" s="24"/>
+    </row>
+    <row r="39" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="23" t="s">
+        <v>93</v>
+      </c>
+      <c r="B39" s="24" t="s">
+        <v>94</v>
+      </c>
+      <c r="C39" s="24"/>
+      <c r="D39" s="24"/>
+      <c r="E39" s="24"/>
+      <c r="F39" s="24"/>
+      <c r="G39" s="24"/>
+    </row>
+    <row r="41" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="B41" s="6"/>
+      <c r="C41" s="6"/>
+      <c r="D41" s="6"/>
+      <c r="E41" s="6"/>
+      <c r="F41" s="6"/>
+      <c r="G41" s="6"/>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B42" s="6"/>
+      <c r="C42" s="6"/>
+      <c r="D42" s="6"/>
+      <c r="E42" s="6"/>
+      <c r="F42" s="6"/>
+      <c r="G42" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="26">
+  <mergeCells count="31">
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="B7:G7"/>
@@ -1679,11 +1985,16 @@
     <mergeCell ref="A24:E24"/>
     <mergeCell ref="A25:E25"/>
     <mergeCell ref="A26:E26"/>
-    <mergeCell ref="A27:E27"/>
-    <mergeCell ref="A28:E28"/>
-    <mergeCell ref="A29:G31"/>
-    <mergeCell ref="A33:G33"/>
-    <mergeCell ref="A34:G34"/>
+    <mergeCell ref="B27:G27"/>
+    <mergeCell ref="A29:E29"/>
+    <mergeCell ref="A30:E30"/>
+    <mergeCell ref="A31:G33"/>
+    <mergeCell ref="B34:G34"/>
+    <mergeCell ref="A37:G37"/>
+    <mergeCell ref="B38:G38"/>
+    <mergeCell ref="B39:G39"/>
+    <mergeCell ref="A41:G41"/>
+    <mergeCell ref="A42:G42"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1700,7 +2011,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:G26"/>
+  <dimension ref="A1:G32"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
@@ -1711,7 +2022,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -1721,7 +2032,7 @@
     </row>
     <row r="4" customFormat="false" ht="78.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>81</v>
+        <v>97</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -1732,7 +2043,7 @@
     </row>
     <row r="5" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -1743,10 +2054,10 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="16" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="C7" s="16"/>
       <c r="D7" s="16"/>
@@ -1755,11 +2066,11 @@
       <c r="G7" s="16"/>
     </row>
     <row r="8" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="20" t="s">
-        <v>83</v>
+      <c r="A8" s="25" t="s">
+        <v>99</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="C8" s="7"/>
       <c r="D8" s="7"/>
@@ -1768,11 +2079,11 @@
       <c r="G8" s="7"/>
     </row>
     <row r="9" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="20" t="s">
-        <v>85</v>
+      <c r="A9" s="25" t="s">
+        <v>101</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
@@ -1781,11 +2092,11 @@
       <c r="G9" s="7"/>
     </row>
     <row r="10" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="20" t="s">
-        <v>87</v>
+      <c r="A10" s="25" t="s">
+        <v>103</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>88</v>
+        <v>104</v>
       </c>
       <c r="C10" s="7"/>
       <c r="D10" s="7"/>
@@ -1794,11 +2105,11 @@
       <c r="G10" s="7"/>
     </row>
     <row r="11" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="20" t="s">
-        <v>89</v>
+      <c r="A11" s="25" t="s">
+        <v>105</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="C11" s="7"/>
       <c r="D11" s="7"/>
@@ -1807,11 +2118,11 @@
       <c r="G11" s="7"/>
     </row>
     <row r="12" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="20" t="s">
-        <v>91</v>
+      <c r="A12" s="25" t="s">
+        <v>107</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>92</v>
+        <v>108</v>
       </c>
       <c r="C12" s="7"/>
       <c r="D12" s="7"/>
@@ -1820,11 +2131,11 @@
       <c r="G12" s="7"/>
     </row>
     <row r="13" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="20" t="s">
-        <v>93</v>
+      <c r="A13" s="25" t="s">
+        <v>109</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>94</v>
+        <v>110</v>
       </c>
       <c r="C13" s="7"/>
       <c r="D13" s="7"/>
@@ -1849,13 +2160,13 @@
     </row>
     <row r="16" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="7" t="s">
-        <v>95</v>
+        <v>111</v>
       </c>
       <c r="B16" s="7"/>
       <c r="C16" s="7"/>
       <c r="D16" s="7"/>
       <c r="E16" s="7"/>
-      <c r="F16" s="18"/>
+      <c r="F16" s="20"/>
       <c r="G16" s="17" t="str">
         <f aca="false">IF(F16="","",IF(UPPER(TRIM(F16))="B","Riktig","Prøv igjen"))</f>
         <v/>
@@ -1863,13 +2174,13 @@
     </row>
     <row r="17" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="7" t="s">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="B17" s="7"/>
       <c r="C17" s="7"/>
       <c r="D17" s="7"/>
       <c r="E17" s="7"/>
-      <c r="F17" s="18"/>
+      <c r="F17" s="20"/>
       <c r="G17" s="17" t="str">
         <f aca="false">IF(F17="","",IF(UPPER(TRIM(F17))="A","Riktig","Prøv igjen"))</f>
         <v/>
@@ -1877,13 +2188,13 @@
     </row>
     <row r="18" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>97</v>
+        <v>113</v>
       </c>
       <c r="B18" s="7"/>
       <c r="C18" s="7"/>
       <c r="D18" s="7"/>
       <c r="E18" s="7"/>
-      <c r="F18" s="18"/>
+      <c r="F18" s="20"/>
       <c r="G18" s="17" t="str">
         <f aca="false">IF(F18="","",IF(UPPER(TRIM(F18))="A","Riktig","Prøv igjen"))</f>
         <v/>
@@ -1891,13 +2202,13 @@
     </row>
     <row r="19" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="7" t="s">
-        <v>98</v>
+        <v>114</v>
       </c>
       <c r="B19" s="7"/>
       <c r="C19" s="7"/>
       <c r="D19" s="7"/>
       <c r="E19" s="7"/>
-      <c r="F19" s="18"/>
+      <c r="F19" s="20"/>
       <c r="G19" s="17" t="str">
         <f aca="false">IF(F19="","",IF(UPPER(TRIM(F19))="C","Riktig","Prøv igjen"))</f>
         <v/>
@@ -1905,7 +2216,7 @@
     </row>
     <row r="20" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="7" t="s">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="B20" s="7"/>
       <c r="C20" s="7"/>
@@ -1913,56 +2224,106 @@
       <c r="E20" s="7"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="19"/>
-      <c r="B21" s="19"/>
-      <c r="C21" s="19"/>
-      <c r="D21" s="19"/>
-      <c r="E21" s="19"/>
-      <c r="F21" s="19"/>
-      <c r="G21" s="19"/>
+      <c r="A21" s="21"/>
+      <c r="B21" s="21"/>
+      <c r="C21" s="21"/>
+      <c r="D21" s="21"/>
+      <c r="E21" s="21"/>
+      <c r="F21" s="21"/>
+      <c r="G21" s="21"/>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="19"/>
-      <c r="B22" s="19"/>
-      <c r="C22" s="19"/>
-      <c r="D22" s="19"/>
-      <c r="E22" s="19"/>
-      <c r="F22" s="19"/>
-      <c r="G22" s="19"/>
+      <c r="A22" s="21"/>
+      <c r="B22" s="21"/>
+      <c r="C22" s="21"/>
+      <c r="D22" s="21"/>
+      <c r="E22" s="21"/>
+      <c r="F22" s="21"/>
+      <c r="G22" s="21"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="19"/>
-      <c r="B23" s="19"/>
-      <c r="C23" s="19"/>
-      <c r="D23" s="19"/>
-      <c r="E23" s="19"/>
-      <c r="F23" s="19"/>
-      <c r="G23" s="19"/>
-    </row>
-    <row r="25" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="6" t="s">
-        <v>100</v>
-      </c>
-      <c r="B25" s="6"/>
-      <c r="C25" s="6"/>
-      <c r="D25" s="6"/>
-      <c r="E25" s="6"/>
-      <c r="F25" s="6"/>
-      <c r="G25" s="6"/>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="B26" s="6"/>
-      <c r="C26" s="6"/>
-      <c r="D26" s="6"/>
-      <c r="E26" s="6"/>
-      <c r="F26" s="6"/>
-      <c r="G26" s="6"/>
+      <c r="A23" s="21"/>
+      <c r="B23" s="21"/>
+      <c r="C23" s="21"/>
+      <c r="D23" s="21"/>
+      <c r="E23" s="21"/>
+      <c r="F23" s="21"/>
+      <c r="G23" s="21"/>
+    </row>
+    <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="B24" s="19" t="s">
+        <v>116</v>
+      </c>
+      <c r="C24" s="19"/>
+      <c r="D24" s="19"/>
+      <c r="E24" s="19"/>
+      <c r="F24" s="19"/>
+      <c r="G24" s="19"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="22" t="s">
+        <v>50</v>
+      </c>
+      <c r="B27" s="22"/>
+      <c r="C27" s="22"/>
+      <c r="D27" s="22"/>
+      <c r="E27" s="22"/>
+      <c r="F27" s="22"/>
+      <c r="G27" s="22"/>
+    </row>
+    <row r="28" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="23" t="s">
+        <v>117</v>
+      </c>
+      <c r="B28" s="24" t="s">
+        <v>118</v>
+      </c>
+      <c r="C28" s="24"/>
+      <c r="D28" s="24"/>
+      <c r="E28" s="24"/>
+      <c r="F28" s="24"/>
+      <c r="G28" s="24"/>
+    </row>
+    <row r="29" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="23" t="s">
+        <v>119</v>
+      </c>
+      <c r="B29" s="24" t="s">
+        <v>120</v>
+      </c>
+      <c r="C29" s="24"/>
+      <c r="D29" s="24"/>
+      <c r="E29" s="24"/>
+      <c r="F29" s="24"/>
+      <c r="G29" s="24"/>
+    </row>
+    <row r="31" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="6" t="s">
+        <v>121</v>
+      </c>
+      <c r="B31" s="6"/>
+      <c r="C31" s="6"/>
+      <c r="D31" s="6"/>
+      <c r="E31" s="6"/>
+      <c r="F31" s="6"/>
+      <c r="G31" s="6"/>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B32" s="6"/>
+      <c r="C32" s="6"/>
+      <c r="D32" s="6"/>
+      <c r="E32" s="6"/>
+      <c r="F32" s="6"/>
+      <c r="G32" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="18">
+  <mergeCells count="22">
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="B7:G7"/>
@@ -1979,8 +2340,12 @@
     <mergeCell ref="A19:E19"/>
     <mergeCell ref="A20:E20"/>
     <mergeCell ref="A21:G23"/>
-    <mergeCell ref="A25:G25"/>
-    <mergeCell ref="A26:G26"/>
+    <mergeCell ref="B24:G24"/>
+    <mergeCell ref="A27:G27"/>
+    <mergeCell ref="B28:G28"/>
+    <mergeCell ref="B29:G29"/>
+    <mergeCell ref="A31:G31"/>
+    <mergeCell ref="A32:G32"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1997,7 +2362,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:G28"/>
+  <dimension ref="A1:G40"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="34"/>
@@ -2008,7 +2373,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>101</v>
+        <v>122</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -2018,7 +2383,7 @@
     </row>
     <row r="4" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="6" t="s">
-        <v>102</v>
+        <v>123</v>
       </c>
       <c r="B4" s="6"/>
       <c r="C4" s="6"/>
@@ -2029,7 +2394,7 @@
     </row>
     <row r="5" customFormat="false" ht="78.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="7" t="s">
-        <v>103</v>
+        <v>124</v>
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
@@ -2040,10 +2405,10 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="16" t="s">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="B7" s="16" t="s">
-        <v>51</v>
+        <v>61</v>
       </c>
       <c r="C7" s="16"/>
       <c r="D7" s="16"/>
@@ -2052,11 +2417,11 @@
       <c r="G7" s="16"/>
     </row>
     <row r="8" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="20" t="s">
-        <v>104</v>
+      <c r="A8" s="25" t="s">
+        <v>125</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>105</v>
+        <v>126</v>
       </c>
       <c r="C8" s="7"/>
       <c r="D8" s="7"/>
@@ -2065,11 +2430,11 @@
       <c r="G8" s="7"/>
     </row>
     <row r="9" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="20" t="s">
-        <v>106</v>
+      <c r="A9" s="25" t="s">
+        <v>127</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>107</v>
+        <v>128</v>
       </c>
       <c r="C9" s="7"/>
       <c r="D9" s="7"/>
@@ -2078,11 +2443,11 @@
       <c r="G9" s="7"/>
     </row>
     <row r="10" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="20" t="s">
-        <v>108</v>
+      <c r="A10" s="25" t="s">
+        <v>129</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>109</v>
+        <v>130</v>
       </c>
       <c r="C10" s="7"/>
       <c r="D10" s="7"/>
@@ -2091,11 +2456,11 @@
       <c r="G10" s="7"/>
     </row>
     <row r="11" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="20" t="s">
-        <v>110</v>
+      <c r="A11" s="25" t="s">
+        <v>131</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>111</v>
+        <v>132</v>
       </c>
       <c r="C11" s="7"/>
       <c r="D11" s="7"/>
@@ -2104,11 +2469,11 @@
       <c r="G11" s="7"/>
     </row>
     <row r="12" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="20" t="s">
-        <v>112</v>
+      <c r="A12" s="25" t="s">
+        <v>133</v>
       </c>
       <c r="B12" s="7" t="s">
-        <v>113</v>
+        <v>134</v>
       </c>
       <c r="C12" s="7"/>
       <c r="D12" s="7"/>
@@ -2117,11 +2482,11 @@
       <c r="G12" s="7"/>
     </row>
     <row r="13" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="20" t="s">
-        <v>114</v>
+      <c r="A13" s="25" t="s">
+        <v>135</v>
       </c>
       <c r="B13" s="7" t="s">
-        <v>115</v>
+        <v>136</v>
       </c>
       <c r="C13" s="7"/>
       <c r="D13" s="7"/>
@@ -2130,11 +2495,11 @@
       <c r="G13" s="7"/>
     </row>
     <row r="14" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="20" t="s">
-        <v>58</v>
+      <c r="A14" s="25" t="s">
+        <v>68</v>
       </c>
       <c r="B14" s="7" t="s">
-        <v>116</v>
+        <v>137</v>
       </c>
       <c r="C14" s="7"/>
       <c r="D14" s="7"/>
@@ -2143,11 +2508,11 @@
       <c r="G14" s="7"/>
     </row>
     <row r="15" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="20" t="s">
-        <v>60</v>
+      <c r="A15" s="25" t="s">
+        <v>70</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>117</v>
+        <v>138</v>
       </c>
       <c r="C15" s="7"/>
       <c r="D15" s="7"/>
@@ -2172,7 +2537,7 @@
     </row>
     <row r="18" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>118</v>
+        <v>139</v>
       </c>
       <c r="B18" s="7"/>
       <c r="C18" s="7"/>
@@ -2184,78 +2549,67 @@
         <v/>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="7" t="s">
-        <v>119</v>
-      </c>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="15"/>
-      <c r="G19" s="17" t="str">
-        <f aca="false">IF(F19="","",IF(ABS(F19-(92))&lt;=0.000000001,"Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="7" t="s">
-        <v>120</v>
-      </c>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="15"/>
-      <c r="G20" s="17" t="str">
-        <f aca="false">IF(F20="","",IF(ABS(F20-(91.7))&lt;=0.1,"Riktig","Prøv igjen"))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="19" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="B19" s="19" t="s">
+        <v>140</v>
+      </c>
+      <c r="C19" s="19"/>
+      <c r="D19" s="19"/>
+      <c r="E19" s="19"/>
+      <c r="F19" s="19"/>
+      <c r="G19" s="19"/>
+    </row>
+    <row r="21" customFormat="false" ht="18.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="7" t="s">
-        <v>121</v>
+        <v>141</v>
       </c>
       <c r="B21" s="7"/>
       <c r="C21" s="7"/>
       <c r="D21" s="7"/>
       <c r="E21" s="7"/>
-      <c r="F21" s="18"/>
+      <c r="F21" s="15"/>
       <c r="G21" s="17" t="str">
-        <f aca="false">IF(F21="","",IF(UPPER(TRIM(F21))="B","Riktig","Prøv igjen"))</f>
+        <f aca="false">IF(F21="","",IF(ABS(F21-(92))&lt;=0.000000001,"Riktig","Prøv igjen"))</f>
         <v/>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="7" t="s">
-        <v>122</v>
-      </c>
-      <c r="B22" s="7"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-    </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="19"/>
-      <c r="B23" s="19"/>
-      <c r="C23" s="19"/>
-      <c r="D23" s="19"/>
-      <c r="E23" s="19"/>
-      <c r="F23" s="19"/>
-      <c r="G23" s="19"/>
-    </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="19"/>
-      <c r="B24" s="19"/>
-      <c r="C24" s="19"/>
-      <c r="D24" s="19"/>
-      <c r="E24" s="19"/>
-      <c r="F24" s="19"/>
-      <c r="G24" s="19"/>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="19"/>
-      <c r="B25" s="19"/>
+    <row r="22" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="B22" s="19" t="s">
+        <v>142</v>
+      </c>
+      <c r="C22" s="19"/>
+      <c r="D22" s="19"/>
+      <c r="E22" s="19"/>
+      <c r="F22" s="19"/>
+      <c r="G22" s="19"/>
+    </row>
+    <row r="24" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="B24" s="7"/>
+      <c r="C24" s="7"/>
+      <c r="D24" s="7"/>
+      <c r="E24" s="7"/>
+      <c r="F24" s="15"/>
+      <c r="G24" s="17" t="str">
+        <f aca="false">IF(F24="","",IF(ABS(F24-(91.7))&lt;=0.1,"Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="B25" s="19" t="s">
+        <v>144</v>
+      </c>
       <c r="C25" s="19"/>
       <c r="D25" s="19"/>
       <c r="E25" s="19"/>
@@ -2263,29 +2617,129 @@
       <c r="G25" s="19"/>
     </row>
     <row r="27" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="6" t="s">
-        <v>123</v>
-      </c>
-      <c r="B27" s="6"/>
-      <c r="C27" s="6"/>
-      <c r="D27" s="6"/>
-      <c r="E27" s="6"/>
-      <c r="F27" s="6"/>
-      <c r="G27" s="6"/>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="6" t="s">
-        <v>46</v>
-      </c>
-      <c r="B28" s="6"/>
-      <c r="C28" s="6"/>
-      <c r="D28" s="6"/>
-      <c r="E28" s="6"/>
-      <c r="F28" s="6"/>
-      <c r="G28" s="6"/>
+      <c r="A27" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="B27" s="7"/>
+      <c r="C27" s="7"/>
+      <c r="D27" s="7"/>
+      <c r="E27" s="7"/>
+      <c r="F27" s="20"/>
+      <c r="G27" s="17" t="str">
+        <f aca="false">IF(F27="","",IF(UPPER(TRIM(F27))="B","Riktig","Prøv igjen"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="B28" s="7"/>
+      <c r="C28" s="7"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="7"/>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="21"/>
+      <c r="B29" s="21"/>
+      <c r="C29" s="21"/>
+      <c r="D29" s="21"/>
+      <c r="E29" s="21"/>
+      <c r="F29" s="21"/>
+      <c r="G29" s="21"/>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="21"/>
+      <c r="B30" s="21"/>
+      <c r="C30" s="21"/>
+      <c r="D30" s="21"/>
+      <c r="E30" s="21"/>
+      <c r="F30" s="21"/>
+      <c r="G30" s="21"/>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="21"/>
+      <c r="B31" s="21"/>
+      <c r="C31" s="21"/>
+      <c r="D31" s="21"/>
+      <c r="E31" s="21"/>
+      <c r="F31" s="21"/>
+      <c r="G31" s="21"/>
+    </row>
+    <row r="32" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="B32" s="19" t="s">
+        <v>147</v>
+      </c>
+      <c r="C32" s="19"/>
+      <c r="D32" s="19"/>
+      <c r="E32" s="19"/>
+      <c r="F32" s="19"/>
+      <c r="G32" s="19"/>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="22" t="s">
+        <v>50</v>
+      </c>
+      <c r="B35" s="22"/>
+      <c r="C35" s="22"/>
+      <c r="D35" s="22"/>
+      <c r="E35" s="22"/>
+      <c r="F35" s="22"/>
+      <c r="G35" s="22"/>
+    </row>
+    <row r="36" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="23" t="s">
+        <v>148</v>
+      </c>
+      <c r="B36" s="24" t="s">
+        <v>149</v>
+      </c>
+      <c r="C36" s="24"/>
+      <c r="D36" s="24"/>
+      <c r="E36" s="24"/>
+      <c r="F36" s="24"/>
+      <c r="G36" s="24"/>
+    </row>
+    <row r="37" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="23" t="s">
+        <v>150</v>
+      </c>
+      <c r="B37" s="24" t="s">
+        <v>151</v>
+      </c>
+      <c r="C37" s="24"/>
+      <c r="D37" s="24"/>
+      <c r="E37" s="24"/>
+      <c r="F37" s="24"/>
+      <c r="G37" s="24"/>
+    </row>
+    <row r="39" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="B39" s="6"/>
+      <c r="C39" s="6"/>
+      <c r="D39" s="6"/>
+      <c r="E39" s="6"/>
+      <c r="F39" s="6"/>
+      <c r="G39" s="6"/>
+    </row>
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="B40" s="6"/>
+      <c r="C40" s="6"/>
+      <c r="D40" s="6"/>
+      <c r="E40" s="6"/>
+      <c r="F40" s="6"/>
+      <c r="G40" s="6"/>
     </row>
   </sheetData>
-  <mergeCells count="20">
+  <mergeCells count="27">
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="B7:G7"/>
@@ -2299,13 +2753,20 @@
     <mergeCell ref="B15:G15"/>
     <mergeCell ref="A17:E17"/>
     <mergeCell ref="A18:E18"/>
-    <mergeCell ref="A19:E19"/>
-    <mergeCell ref="A20:E20"/>
+    <mergeCell ref="B19:G19"/>
     <mergeCell ref="A21:E21"/>
-    <mergeCell ref="A22:E22"/>
-    <mergeCell ref="A23:G25"/>
-    <mergeCell ref="A27:G27"/>
-    <mergeCell ref="A28:G28"/>
+    <mergeCell ref="B22:G22"/>
+    <mergeCell ref="A24:E24"/>
+    <mergeCell ref="B25:G25"/>
+    <mergeCell ref="A27:E27"/>
+    <mergeCell ref="A28:E28"/>
+    <mergeCell ref="A29:G31"/>
+    <mergeCell ref="B32:G32"/>
+    <mergeCell ref="A35:G35"/>
+    <mergeCell ref="B36:G36"/>
+    <mergeCell ref="B37:G37"/>
+    <mergeCell ref="A39:G39"/>
+    <mergeCell ref="A40:G40"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/pensum/ma03/MA03_Klasseoppgaver_v5.xlsx
+++ b/pensum/ma03/MA03_Klasseoppgaver_v5.xlsx
@@ -110,13 +110,13 @@
     <t xml:space="preserve">Solcelleanlegg, antall</t>
   </si>
   <si>
-    <t xml:space="preserve">Pris per anlegg, kr uten mva</t>
+    <t xml:space="preserve">Pris per anlegg, kr uten merverdiavgift</t>
   </si>
   <si>
     <t xml:space="preserve">Ladepunkt, antall</t>
   </si>
   <si>
-    <t xml:space="preserve">Pris per ladepunkt, kr uten mva</t>
+    <t xml:space="preserve">Pris per ladepunkt, kr uten merverdiavgift</t>
   </si>
   <si>
     <t xml:space="preserve">Montørtimer per anlegg / ladepunkt</t>
@@ -170,7 +170,7 @@
     <t xml:space="preserve">d)  Kari har skrevet tre setninger om avdelingen. Hvilken av dem er et markedsmål etter lærebokas krav (tallfestet, realistisk, hierarkisk, i samsvar)?   A: «Vi skal bli den foretrukne leverandøren av solceller i bydelen.»   B: «Vi skal selge 42 solcelleanlegg i år, mot 34 i fjor. Ida følger opp hver måned.»   C: «Vi skal satse mer på borettslag, for der ligger pengene.»   (skriv bokstaven)</t>
   </si>
   <si>
-    <t xml:space="preserve">e)  Nye solkraftanlegg i Norge falt fra 149 MW i 2024 til 117 MW i 2025 (−21,5 %). Er delmålet på 42 solcelleanlegg realistisk? Skriv to setninger og ett tiltak.</t>
+    <t xml:space="preserve">e)  Nye solkraftanlegg i Norge falt fra 149 megawatt i 2024 til 117 megawatt i 2025 (−21,5 %). Er delmålet på 42 solcelleanlegg realistisk? Skriv to setninger og ett tiltak.</t>
   </si>
   <si>
     <t xml:space="preserve">Realistiske markedsmål (Markedsføring 3.4); markedsplanen må revideres jevnlig (innledningen til kap. 3). Dekningsbidrag per knapp faktor er fra Økonomistyring kap. 7, ikke fra Markedsføring kap. 3.</t>
@@ -221,7 +221,7 @@
     <t xml:space="preserve">Kapasitet og pris</t>
   </si>
   <si>
-    <t xml:space="preserve">3 500 fakturerbare timer i året, 890 kr per time uten mva</t>
+    <t xml:space="preserve">3 500 fakturerbare timer i året, 890 kr per time uten merverdiavgift</t>
   </si>
   <si>
     <t xml:space="preserve">Marked i dag</t>
@@ -311,7 +311,7 @@
     <t xml:space="preserve">Fjells antall delt på hele markedet, ganger 100: 48 av 1 600. Forretningsidéen: se etter setningen som har produkt, marked og særpreg.</t>
   </si>
   <si>
-    <t xml:space="preserve">Kilde: Hjertnes, F.: Markedsføring, organisasjon og ledelse for LØM-emnet, kap. 3, avsnitt 3.2 (forretningsidé) og 3.3 (situasjonsanalyse), kap. 10.2 (SOFT-analyse). Elbilandelen: Elbilforeningen, årsberetning 2025. Fjell Elektro AS er en konstruert casebedrift; markedstallene for Oslo øst er konstruerte.</t>
+    <t xml:space="preserve">Kilde: Hjertnes, F.: Markedsføring, organisasjon og ledelse for LØM-emnet, kap. 3, avsnitt 3.2 (forretningsidé) og 3.3 (situasjonsanalyse), kap. 10.2 (analysen av sterke og svake sider, muligheter og trusler). Elbilandelen: Elbilforeningen, årsberetning 2025. Fjell Elektro AS er en konstruert casebedrift; markedstallene for Oslo øst er konstruerte.</t>
   </si>
   <si>
     <t xml:space="preserve">B1 · Nordlys: fire nye veier å vokse, og én profil</t>
@@ -1205,7 +1205,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="12" t="s">
         <v>28</v>
       </c>
@@ -1227,7 +1227,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="12" t="s">
         <v>30</v>
       </c>
@@ -1940,7 +1940,7 @@
       <c r="F39" s="24"/>
       <c r="G39" s="24"/>
     </row>
-    <row r="41" customFormat="false" ht="48.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="41" customFormat="false" ht="63.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="6" t="s">
         <v>95</v>
       </c>

--- a/pensum/ma03/MA03_Klasseoppgaver_v5.xlsx
+++ b/pensum/ma03/MA03_Klasseoppgaver_v5.xlsx
@@ -26,7 +26,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="153">
   <si>
-    <t xml:space="preserve">Klasseoppgaver til Markedsføring kapittel 3: Markedsplanen (V5)</t>
+    <t xml:space="preserve">Klasseoppgaver til Markedsføring kapittel 3: Markedsplanen (versjon 5)</t>
   </si>
   <si>
     <t xml:space="preserve">LØM · Fagskolen Oslo, Avdeling Elkraft · versjon 5, oktober 2026</t>

--- a/pensum/ma03/MA03_Klasseoppgaver_v5.xlsx
+++ b/pensum/ma03/MA03_Klasseoppgaver_v5.xlsx
@@ -95,7 +95,7 @@
     <t xml:space="preserve">Kort oppsummert: Markedsmål skal være realistiske, hierarkiske, tallfestede og innbyrdes i samsvar (avsnitt 3.4). Hierarkisk betyr ett hovedmål med delmål under. I samsvar betyr at delmålene til sammen bærer hovedmålet: regn delmålene om til kroner og sammenlikn. Realistisk betyr at bedriften har kapasitet til det: regn hvor mange flere timer målet krever.</t>
   </si>
   <si>
-    <t xml:space="preserve">Casen er lagt til 2026/2027. Solcelle- og ladeavdelingen i Nordlys monterte 34 solcelleanlegg og 180 ladepunkt i fjor og omsatte for 3 335 640 kr. Kari har satt hovedmålet for i år: omsetningen skal øke med minst 20 %. Ida har satt delmålene: 42 solcelleanlegg og 215 ladepunkt, med samme priser som i fjor. Et anlegg tar 14 montørtimer og et ladepunkt 2. Nordlys fakturerer 14 400 montørtimer i året. Gå fram slik: regn hovedmålet om til kroner, regn delmålene om til kroner (antall × pris, lagt sammen), sammenlikn, og regn til slutt hvor mange flere montørtimer delmålene krever.</t>
+    <t xml:space="preserve">Casen er lagt til 2026/2027. Solcelle- og ladeavdelingen i Nordlys monterte 34 solcelleanlegg og 180 ladepunkt i fjor og omsatte for 3 335 640 kr. Kari har satt hovedmålet for i år: omsetningen skal øke med minst 20 %. Ida har satt delmålene: 42 solcelleanlegg og 215 ladepunkt, med samme priser som i fjor. Et anlegg tar 14 montørtimer og et ladepunkt 2. Nordlys fakturerer 14 400 montørtimer i året (12 montører × 1 200 timer). Gå fram slik: regn hovedmålet om til kroner, regn delmålene om til kroner (antall × pris, lagt sammen), sammenlikn, og regn til slutt hvor mange flere montørtimer delmålene krever.</t>
   </si>
   <si>
     <t xml:space="preserve">Post</t>
@@ -188,7 +188,7 @@
     <t xml:space="preserve">Timene</t>
   </si>
   <si>
-    <t xml:space="preserve">Regn timene i fjor (34 × 14 + 180 × 2) og ved målet (42 × 14 + 215 × 2). Forskjellen er det målet krever ekstra. Sammenlikn med de 14 400 timene Nordlys fakturerer.</t>
+    <t xml:space="preserve">Regn timene i fjor (34 × 14 + 180 × 2) og ved målet (42 × 14 + 215 × 2). Forskjellen er det målet krever ekstra. Sammenlikn med de 14 400 timene Nordlys fakturerer i året (12 montører × 1 200 timer).</t>
   </si>
   <si>
     <t xml:space="preserve">Kilde: Hjertnes, F.: Markedsføring, organisasjon og ledelse for LØM-emnet, kap. 3, avsnitt 3.4 (markedsmål) og kap. 10.3. Tallene er de samme som i appen og sammendraget til kapittel 3. Nordlys Elektro AS er en konstruert casebedrift.</t>
@@ -434,7 +434,7 @@
     <t xml:space="preserve">Kapasitet</t>
   </si>
   <si>
-    <t xml:space="preserve">3 500 fakturerbare timer i året (to montører og Mona)</t>
+    <t xml:space="preserve">3 500 fakturerbare timer i året (2 montører × 1 400 + Mona 700)</t>
   </si>
   <si>
     <t xml:space="preserve">Driftsmargin 3,0 %</t>
@@ -1461,7 +1461,7 @@
       <c r="F36" s="24"/>
       <c r="G36" s="24"/>
     </row>
-    <row r="37" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="42.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="23" t="s">
         <v>53</v>
       </c>
